--- a/docs/downloads/经营分_鲁东省区__淄博片区_2026-10-18.xlsx
+++ b/docs/downloads/经营分_鲁东省区__淄博片区_2026-10-18.xlsx
@@ -1215,17 +1215,17 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>7279414400891488268</t>
+          <t>7030364676290512900</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IU酒店（淄博高新区高铁北站金科学府店）</t>
+          <t>白玉兰商务酒店（淄博银座广场西六路店）</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>iu酒店·(淄博高新区高铁北站金科学府店)</t>
+          <t>白玉兰商务酒店(淄博银座广场西六路店)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1234,10 +1234,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I8" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1251,19 +1251,19 @@
         <v>10</v>
       </c>
       <c r="M8" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="N8" t="n">
         <v>30</v>
       </c>
       <c r="O8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P8" t="n">
         <v>30</v>
       </c>
       <c r="Q8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R8" t="n">
         <v>30</v>
@@ -1303,17 +1303,17 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>7030364676290512900</t>
+          <t>6783274035129157644</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>白玉兰商务酒店（淄博银座广场西六路店）</t>
+          <t>维也纳酒店(淄博博山易达广场红叶柿岩店)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>白玉兰商务酒店(淄博银座广场西六路店)</t>
+          <t>维也纳酒店(淄博易达广场店)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1339,7 +1339,7 @@
         <v>10</v>
       </c>
       <c r="M9" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="N9" t="n">
         <v>30</v>
@@ -1351,7 +1351,7 @@
         <v>30</v>
       </c>
       <c r="Q9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R9" t="n">
         <v>30</v>
@@ -1391,17 +1391,17 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>6783274035129157644</t>
+          <t>7373164326356289563</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>维也纳酒店(淄博博山易达广场红叶柿岩店)</t>
+          <t>麗枫酒店（淄博人民西路理工大学店）</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>维也纳酒店(淄博易达广场店)</t>
+          <t>丽枫酒店(淄博人民西路店)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1427,7 +1427,7 @@
         <v>10</v>
       </c>
       <c r="M10" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="N10" t="n">
         <v>30</v>
@@ -1439,7 +1439,7 @@
         <v>30</v>
       </c>
       <c r="Q10" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R10" t="n">
         <v>30</v>
@@ -1479,26 +1479,26 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>7373164326356289563</t>
+          <t>7234811944249591808</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>麗枫酒店（淄博人民西路理工大学店）</t>
+          <t>7天优品Premium(淄博临淄大院齐文化博物馆店)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>丽枫酒店(淄博人民西路店)</t>
+          <t>7天优品Premium(淄博临淄区稷山路店)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1515,19 +1515,19 @@
         <v>10</v>
       </c>
       <c r="M11" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N11" t="n">
         <v>30</v>
       </c>
       <c r="O11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P11" t="n">
         <v>30</v>
       </c>
       <c r="Q11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R11" t="n">
         <v>30</v>
@@ -1567,17 +1567,17 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>7165134379755243557</t>
+          <t>6878582251337041927</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>麗枫酒店（淄博沂源螳螂河东路店）</t>
+          <t>7天优品（淄博沂源店）</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>麗枫酒店(淄博沂源螳螂河东路店)</t>
+          <t>7天优品(淄博沂源店)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1586,7 +1586,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1603,7 +1603,7 @@
         <v>10</v>
       </c>
       <c r="M12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N12" t="n">
         <v>30</v>
@@ -1615,7 +1615,7 @@
         <v>30</v>
       </c>
       <c r="Q12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R12" t="n">
         <v>30</v>
@@ -1655,22 +1655,22 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>7234811944249591808</t>
+          <t>6601148776130283527</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>7天优品Premium(淄博临淄大院齐文化博物馆店)</t>
+          <t>7天优品（淄博淄川鸿泰店）</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>7天优品Premium(淄博临淄区稷山路店)</t>
+          <t>7天优品(淄博淄川鸿泰店)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -1697,13 +1697,13 @@
         <v>30</v>
       </c>
       <c r="O13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P13" t="n">
         <v>30</v>
       </c>
       <c r="Q13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R13" t="n">
         <v>30</v>
@@ -1743,17 +1743,17 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>6878582251337041927</t>
+          <t>7215501347955673100</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>7天优品（淄博沂源店）</t>
+          <t>7天酒店（新7天淄博市政府八大局店）</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>7天优品(淄博沂源店)</t>
+          <t>7天酒店(淄博市政府八大局店)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1831,17 +1831,17 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>6601148776130283527</t>
+          <t>7281879252234930211</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>7天优品（淄博淄川鸿泰店）</t>
+          <t>IU酒店（淄博北站裕民路店）</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>7天优品(淄博淄川鸿泰店)</t>
+          <t>IU酒店(淄博高新区裕民路店)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1867,13 +1867,13 @@
         <v>10</v>
       </c>
       <c r="M15" t="n">
+        <v>20</v>
+      </c>
+      <c r="N15" t="n">
+        <v>30</v>
+      </c>
+      <c r="O15" t="n">
         <v>25</v>
-      </c>
-      <c r="N15" t="n">
-        <v>30</v>
-      </c>
-      <c r="O15" t="n">
-        <v>20</v>
       </c>
       <c r="P15" t="n">
         <v>30</v>
@@ -1919,17 +1919,17 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>7215501347955673100</t>
+          <t>7325369309767665674</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>7天酒店（新7天淄博市政府八大局店）</t>
+          <t>IU酒店（淄博淄川区政府蒲松龄故居店）</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>7天酒店(淄博市政府八大局店)</t>
+          <t>IU酒店(淄博淄川松龄东路店)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1941,7 +1941,7 @@
         <v>95</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1955,13 +1955,13 @@
         <v>10</v>
       </c>
       <c r="M16" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="N16" t="n">
         <v>30</v>
       </c>
       <c r="O16" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P16" t="n">
         <v>30</v>
@@ -2007,22 +2007,22 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>7281879252234930211</t>
+          <t>7279414400891488268</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>IU酒店（淄博北站裕民路店）</t>
+          <t>IU酒店（淄博高新区高铁北站金科学府店）</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>IU酒店(淄博高新区裕民路店)</t>
+          <t>iu酒店·(淄博高新区高铁北站金科学府店)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -2095,17 +2095,17 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>7325369309767665674</t>
+          <t>7464475907667789874</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>IU酒店（淄博淄川区政府蒲松龄故居店）</t>
+          <t>锦江之星(淄博周村古商城区政府银座店)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>IU酒店(淄博淄川松龄东路店)</t>
+          <t>锦江之星(淄博周村古商城银座店)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2117,7 +2117,7 @@
         <v>95</v>
       </c>
       <c r="I18" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -2131,13 +2131,13 @@
         <v>10</v>
       </c>
       <c r="M18" t="n">
+        <v>20</v>
+      </c>
+      <c r="N18" t="n">
+        <v>30</v>
+      </c>
+      <c r="O18" t="n">
         <v>25</v>
-      </c>
-      <c r="N18" t="n">
-        <v>30</v>
-      </c>
-      <c r="O18" t="n">
-        <v>20</v>
       </c>
       <c r="P18" t="n">
         <v>30</v>
@@ -2183,55 +2183,55 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>6642980290828519437</t>
+          <t>6601158197904410627</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>希岸酒店（淄博山东理工大学东校店）</t>
+          <t>7天酒店（新7天淄博东四路盛世新城店）</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>希岸酒店(淄博山东理工大学东校店)</t>
+          <t>7天酒店(淄博东四路盛世新城店【新7天】)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>搭门店,稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L19" t="n">
         <v>10</v>
       </c>
       <c r="M19" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N19" t="n">
         <v>30</v>
       </c>
       <c r="O19" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P19" t="n">
         <v>30</v>
       </c>
       <c r="Q19" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R19" t="n">
         <v>30</v>
@@ -2271,17 +2271,17 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>6601158197904410627</t>
+          <t>7320227686423463990</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>7天酒店（新7天淄博东四路盛世新城店）</t>
+          <t>7天酒店（淄博火车站万象汇八大局店）</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>7天酒店(淄博东四路盛世新城店【新7天】)</t>
+          <t>7天酒店(淄博火车站万象汇八大局店)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2290,24 +2290,24 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>搭门店,稳房源,提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L20" t="n">
         <v>10</v>
       </c>
       <c r="M20" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="N20" t="n">
         <v>30</v>
@@ -2623,17 +2623,17 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>7606927714712291391</t>
+          <t>7165134379755243557</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>7天酒店智选版（淄博沂源健康路店）</t>
+          <t>麗枫酒店（淄博沂源螳螂河东路店）</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>7天酒店(淄博沂源健康路店)</t>
+          <t>麗枫酒店(淄博沂源螳螂河东路店)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2642,10 +2642,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I24" t="n">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         <v>10</v>
       </c>
       <c r="M24" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="N24" t="n">
         <v>30</v>
@@ -2671,7 +2671,7 @@
         <v>30</v>
       </c>
       <c r="Q24" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R24" t="n">
         <v>30</v>
@@ -2704,20 +2704,24 @@
           <t>淄博片区</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>淄博市</t>
+        </is>
+      </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>7329425248326813737</t>
+          <t>7606927714712291391</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>IU酒店(淄博临淄金山店)</t>
+          <t>7天酒店智选版（淄博沂源健康路店）</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>IU酒店(淄博临淄金山店)</t>
+          <t>7天酒店(淄博沂源健康路店)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2729,11 +2733,11 @@
         <v>100</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -2743,19 +2747,19 @@
         <v>10</v>
       </c>
       <c r="M25" t="n">
+        <v>20</v>
+      </c>
+      <c r="N25" t="n">
+        <v>30</v>
+      </c>
+      <c r="O25" t="n">
         <v>25</v>
       </c>
-      <c r="N25" t="n">
-        <v>30</v>
-      </c>
-      <c r="O25" t="n">
-        <v>30</v>
-      </c>
       <c r="P25" t="n">
         <v>30</v>
       </c>
       <c r="Q25" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="R25" t="n">
         <v>30</v>
@@ -2788,24 +2792,20 @@
           <t>淄博片区</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>淄博市</t>
-        </is>
-      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>7364265482515384374</t>
+          <t>7329425248326813737</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>IU酒店（淄博八大局中润大道银泰城店）</t>
+          <t>IU酒店(淄博临淄金山店)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>IU酒店(淄博中润大道银泰城店)</t>
+          <t>IU酒店(淄博临淄金山店)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -2837,13 +2837,13 @@
         <v>30</v>
       </c>
       <c r="O26" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P26" t="n">
         <v>30</v>
       </c>
       <c r="Q26" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R26" t="n">
         <v>30</v>
@@ -2883,17 +2883,17 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>6829195819078469635</t>
+          <t>7364265482515384374</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>IU酒店（淄博火车站吾悦广场店）</t>
+          <t>IU酒店（淄博八大局中润大道银泰城店）</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>IU酒店(淄博火车站吾悦广场店)</t>
+          <t>IU酒店(淄博中润大道银泰城店)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2919,13 +2919,13 @@
         <v>10</v>
       </c>
       <c r="M27" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N27" t="n">
         <v>30</v>
       </c>
       <c r="O27" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P27" t="n">
         <v>30</v>
@@ -2971,17 +2971,17 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>7316385528541087807</t>
+          <t>6829195819078469635</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>白玉兰商务酒店（淄博新区大学城店）</t>
+          <t>IU酒店（淄博火车站吾悦广场店）</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>白玉兰商务酒店(淄博新区大学城店)</t>
+          <t>IU酒店(淄博火车站吾悦广场店)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2993,11 +2993,11 @@
         <v>100</v>
       </c>
       <c r="I28" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -3007,13 +3007,13 @@
         <v>10</v>
       </c>
       <c r="M28" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N28" t="n">
         <v>30</v>
       </c>
       <c r="O28" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P28" t="n">
         <v>30</v>
@@ -3059,22 +3059,22 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>6625467416447027207</t>
+          <t>6642980290828519437</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>维也纳3好酒店（淄博金晶大道万象汇八大局店）</t>
+          <t>希岸酒店（淄博山东理工大学东校店）</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>维也纳3好酒店(淄博金晶大道万象汇八大局店)</t>
+          <t>希岸酒店(淄博山东理工大学东校店)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -3095,13 +3095,13 @@
         <v>10</v>
       </c>
       <c r="M29" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N29" t="n">
         <v>30</v>
       </c>
       <c r="O29" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P29" t="n">
         <v>30</v>
@@ -3147,17 +3147,17 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>7464475907667789874</t>
+          <t>7316385528541087807</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>锦江之星(淄博周村古商城区政府银座店)</t>
+          <t>白玉兰商务酒店（淄博新区大学城店）</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>锦江之星(淄博周村古商城银座店)</t>
+          <t>白玉兰商务酒店(淄博新区大学城店)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3169,11 +3169,11 @@
         <v>100</v>
       </c>
       <c r="I30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -3183,13 +3183,13 @@
         <v>10</v>
       </c>
       <c r="M30" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="N30" t="n">
         <v>30</v>
       </c>
       <c r="O30" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P30" t="n">
         <v>30</v>
@@ -3235,33 +3235,33 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>6997616463682996261</t>
+          <t>6625467416447027207</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>麗枫酒店(淄博临淄大院区政府店)</t>
+          <t>维也纳3好酒店（淄博金晶大道万象汇八大局店）</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>麗枫酒店(淄博临淄大院区政府店)</t>
+          <t>维也纳3好酒店(淄博金晶大道万象汇八大局店)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H31" t="n">
         <v>100</v>
       </c>
       <c r="I31" t="n">
-        <v>-10</v>
+        <v>5</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -3271,13 +3271,13 @@
         <v>10</v>
       </c>
       <c r="M31" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N31" t="n">
         <v>30</v>
       </c>
       <c r="O31" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P31" t="n">
         <v>30</v>
@@ -3323,33 +3323,33 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>7375032260830496809</t>
+          <t>6997616463682996261</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>麗枫酒店（淄博周村古商城盛世家居广场店）</t>
+          <t>麗枫酒店(淄博临淄大院区政府店)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>麗枫酒店(淄博周村正阳路五洲国际盛世家居广场店)</t>
+          <t>麗枫酒店(淄博临淄大院区政府店)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H32" t="n">
         <v>100</v>
       </c>
       <c r="I32" t="n">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -3359,19 +3359,19 @@
         <v>10</v>
       </c>
       <c r="M32" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N32" t="n">
         <v>30</v>
       </c>
       <c r="O32" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P32" t="n">
         <v>30</v>
       </c>
       <c r="Q32" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R32" t="n">
         <v>30</v>
@@ -3411,17 +3411,17 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>7320227686423463990</t>
+          <t>7375032260830496809</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>7天酒店（淄博火车站万象汇八大局店）</t>
+          <t>麗枫酒店（淄博周村古商城盛世家居广场店）</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>7天酒店(淄博火车站万象汇八大局店)</t>
+          <t>麗枫酒店(淄博周村正阳路五洲国际盛世家居广场店)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3430,10 +3430,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>10</v>
       </c>
       <c r="M33" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N33" t="n">
         <v>30</v>
@@ -3459,7 +3459,7 @@
         <v>30</v>
       </c>
       <c r="Q33" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R33" t="n">
         <v>30</v>
@@ -3499,29 +3499,29 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>6601226741941798920</t>
+          <t>6601140373894989832</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>7天优品（淄博桓台信誉楼店）</t>
+          <t>7天酒店（新7天淄博临淄大院方正2009银座商业中心店）</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>7天优品 ( 淄博桓台信誉楼店)</t>
+          <t>7天酒店(新7天·淄博临淄天齐路方正2009店)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H34" t="n">
         <v>105</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -3541,13 +3541,13 @@
         <v>30</v>
       </c>
       <c r="O34" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P34" t="n">
         <v>30</v>
       </c>
       <c r="Q34" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R34" t="n">
         <v>30</v>
@@ -3587,33 +3587,33 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>6601140373894989832</t>
+          <t>7233752139812571191</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>7天酒店（新7天淄博临淄大院方正2009银座商业中心店）</t>
+          <t>7天酒店（淄博火车站南广场店）</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>7天酒店(新7天·淄博临淄天齐路方正2009店)</t>
+          <t>7天酒店(淄博火车站南广场店)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H35" t="n">
         <v>105</v>
       </c>
       <c r="I35" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>拿收益</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -3629,13 +3629,13 @@
         <v>30</v>
       </c>
       <c r="O35" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P35" t="n">
         <v>30</v>
       </c>
       <c r="Q35" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R35" t="n">
         <v>30</v>
@@ -3675,17 +3675,17 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>7233752139812571191</t>
+          <t>7184741880742021180</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>7天酒店（淄博火车站南广场店）</t>
+          <t>IU酒店（淄博八大局万象汇王府井店）</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>7天酒店(淄博火车站南广场店)</t>
+          <t>IU酒店(淄博万象汇王府井步行街店)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3697,11 +3697,11 @@
         <v>105</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -3711,7 +3711,7 @@
         <v>10</v>
       </c>
       <c r="M36" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N36" t="n">
         <v>30</v>
@@ -3723,7 +3723,7 @@
         <v>30</v>
       </c>
       <c r="Q36" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R36" t="n">
         <v>30</v>
@@ -3763,17 +3763,17 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>7184741880742021180</t>
+          <t>7025086648934303758</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>IU酒店（淄博八大局万象汇王府井店）</t>
+          <t>IU酒店（淄博柳泉路八大局店）</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>IU酒店(淄博万象汇王府井步行街店)</t>
+          <t>IU酒店(淄博柳泉路店)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -3785,7 +3785,7 @@
         <v>105</v>
       </c>
       <c r="I37" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -3799,19 +3799,19 @@
         <v>10</v>
       </c>
       <c r="M37" t="n">
+        <v>20</v>
+      </c>
+      <c r="N37" t="n">
+        <v>30</v>
+      </c>
+      <c r="O37" t="n">
+        <v>30</v>
+      </c>
+      <c r="P37" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q37" t="n">
         <v>25</v>
-      </c>
-      <c r="N37" t="n">
-        <v>30</v>
-      </c>
-      <c r="O37" t="n">
-        <v>30</v>
-      </c>
-      <c r="P37" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>20</v>
       </c>
       <c r="R37" t="n">
         <v>30</v>
@@ -3851,17 +3851,17 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>7025086648934303758</t>
+          <t>7414382110259021833</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>IU酒店（淄博柳泉路八大局店）</t>
+          <t>希岸酒店（淄博临淄区政府火车站店）</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>IU酒店(淄博柳泉路店)</t>
+          <t>希岸酒店(淄博临淄区政府火车站店)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3873,11 +3873,11 @@
         <v>105</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -3887,19 +3887,19 @@
         <v>10</v>
       </c>
       <c r="M38" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="N38" t="n">
         <v>30</v>
       </c>
       <c r="O38" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P38" t="n">
         <v>30</v>
       </c>
       <c r="Q38" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R38" t="n">
         <v>30</v>
@@ -3939,33 +3939,33 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>7414382110259021833</t>
+          <t>6996139025513842719</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>希岸酒店（淄博临淄区政府火车站店）</t>
+          <t>白玉兰商务酒店（淄博桓台信誉楼店）</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>希岸酒店(淄博临淄区政府火车站店)</t>
+          <t>白玉兰商务酒店(淄博桓台信誉楼店)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H39" t="n">
         <v>105</v>
       </c>
       <c r="I39" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -3975,13 +3975,13 @@
         <v>10</v>
       </c>
       <c r="M39" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N39" t="n">
         <v>30</v>
       </c>
       <c r="O39" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P39" t="n">
         <v>30</v>
@@ -4027,17 +4027,17 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>6996139025513842719</t>
+          <t>6601226741941798920</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>白玉兰商务酒店（淄博桓台信誉楼店）</t>
+          <t>7天优品（淄博桓台信誉楼店）</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>白玉兰商务酒店(淄博桓台信誉楼店)</t>
+          <t>7天优品 ( 淄博桓台信誉楼店)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4046,14 +4046,14 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -4063,19 +4063,19 @@
         <v>10</v>
       </c>
       <c r="M40" t="n">
+        <v>30</v>
+      </c>
+      <c r="N40" t="n">
+        <v>30</v>
+      </c>
+      <c r="O40" t="n">
         <v>25</v>
       </c>
-      <c r="N40" t="n">
-        <v>30</v>
-      </c>
-      <c r="O40" t="n">
-        <v>30</v>
-      </c>
       <c r="P40" t="n">
         <v>30</v>
       </c>
       <c r="Q40" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R40" t="n">
         <v>30</v>
@@ -4489,7 +4489,7 @@
         <v>115</v>
       </c>
       <c r="I45" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
